--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -206,7 +206,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2025-08-14T17:15:40.435962+00:00</t>
+    <t>2025-08-21T08:01:19.644250+00:00</t>
   </si>
   <si>
     <t>Number of techniques</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -10542,7 +10542,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2025-09-24T14:43:34.554803+00:00</t>
+    <t>2025-09-29T14:23:33.968458+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -8406,7 +8406,7 @@
     <t>In weakness</t>
   </si>
   <si>
-    <t>Weakness occurances</t>
+    <t>Weakness occurrences</t>
   </si>
   <si>
     <t>Crime scene searching
@@ -9593,7 +9593,13 @@
     <t>This search may be conducted live, directly over the data, or from a generated index of strings extracted from the data. The words searched for may be either case-specific, or sometimes case-type specific.</t>
   </si>
   <si>
-    <t>['T1125:Keyword search (live)', 'T1126:Keyword search (live) (physical)', 'T1127:Keyword search (live) (logical)', 'T1124:Keyword search (indexed)', 'T1121:Keyword indexing', 'T1122:Keyword search (case-type wordlists)', 'T1123:Keyword search (case-specific wordlists)']</t>
+    <t>['T1125:Keyword search (live)',
+ 'T1126:Keyword search (live) (physical)',
+ 'T1127:Keyword search (live) (logical)',
+ 'T1124:Keyword search (indexed)',
+ 'T1121:Keyword indexing',
+ 'T1122:Keyword search (case-type wordlists)',
+ 'T1123:Keyword search (case-specific wordlists)']</t>
   </si>
   <si>
     <t>M1035, M1036</t>
@@ -10542,7 +10548,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2025-09-29T14:23:33.968458+00:00</t>
+    <t>2025-10-03T07:56:04.649046+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>
@@ -11681,7 +11687,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1532</v>
       </c>
     </row>
@@ -11697,7 +11703,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12084,7 +12090,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12100,7 +12106,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12236,7 +12242,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12252,7 +12258,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12388,7 +12394,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12404,7 +12410,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12540,7 +12546,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12556,7 +12562,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12692,7 +12698,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12708,7 +12714,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12844,7 +12850,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12860,7 +12866,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -12985,7 +12991,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13001,7 +13007,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13137,7 +13143,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13153,7 +13159,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13298,7 +13304,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13314,7 +13320,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13439,7 +13445,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13455,7 +13461,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13580,7 +13586,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13596,7 +13602,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13798,7 +13804,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13814,7 +13820,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13939,7 +13945,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -13955,7 +13961,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14080,7 +14086,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14096,7 +14102,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14221,7 +14227,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14237,7 +14243,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14362,7 +14368,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14378,7 +14384,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14503,7 +14509,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14519,7 +14525,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14644,7 +14650,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14660,7 +14666,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14835,7 +14841,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -14851,7 +14857,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -15006,7 +15012,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -15022,7 +15028,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -15255,7 +15261,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -15271,7 +15277,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -15616,7 +15622,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1545</v>
       </c>
     </row>
@@ -15632,7 +15638,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -15798,7 +15804,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1872</v>
       </c>
     </row>
@@ -15814,7 +15820,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -15989,7 +15995,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16005,7 +16011,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16159,7 +16165,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16175,7 +16181,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16439,7 +16445,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16455,7 +16461,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16667,7 +16673,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16683,7 +16689,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -16915,7 +16921,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1895</v>
       </c>
     </row>
@@ -16931,7 +16937,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -17114,7 +17120,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1901</v>
       </c>
     </row>
@@ -17130,7 +17136,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -17323,7 +17329,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -17339,7 +17345,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -17667,7 +17673,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -17683,7 +17689,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -17919,7 +17925,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -17935,7 +17941,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -18178,7 +18184,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -18194,7 +18200,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -18526,7 +18532,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1922</v>
       </c>
     </row>
@@ -18542,7 +18548,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -18725,7 +18731,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1925</v>
       </c>
     </row>
@@ -18741,7 +18747,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -18934,7 +18940,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1925</v>
       </c>
     </row>
@@ -18950,7 +18956,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19209,7 +19215,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1925</v>
       </c>
     </row>
@@ -19225,7 +19231,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19408,7 +19414,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1938</v>
       </c>
     </row>
@@ -19424,7 +19430,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19549,7 +19555,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19565,7 +19571,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19710,7 +19716,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19726,7 +19732,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19851,7 +19857,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -19867,7 +19873,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -20003,7 +20009,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1948</v>
       </c>
     </row>
@@ -20019,7 +20025,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -20155,7 +20161,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -20171,7 +20177,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21268,7 +21274,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21284,7 +21290,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21420,7 +21426,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21436,7 +21442,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21572,7 +21578,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21588,7 +21594,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21820,7 +21826,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21836,7 +21842,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21961,7 +21967,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -21977,7 +21983,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22241,7 +22247,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22257,7 +22263,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22471,7 +22477,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22487,7 +22493,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22623,7 +22629,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22639,7 +22645,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22916,7 +22922,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -22932,7 +22938,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23198,7 +23204,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23214,7 +23220,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23350,7 +23356,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23366,7 +23372,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23502,7 +23508,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23518,7 +23524,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23840,7 +23846,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -23856,7 +23862,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -24229,7 +24235,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -24245,7 +24251,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -24370,7 +24376,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -24386,7 +24392,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -24522,7 +24528,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -24538,7 +24544,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -26560,7 +26566,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -26576,7 +26582,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -26712,7 +26718,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1604</v>
       </c>
     </row>
@@ -26728,7 +26734,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -26902,7 +26908,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -26918,7 +26924,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27073,7 +27079,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27089,7 +27095,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27225,7 +27231,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27241,7 +27247,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27377,7 +27383,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27393,7 +27399,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27529,7 +27535,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27545,7 +27551,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27681,7 +27687,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27697,7 +27703,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27926,7 +27932,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -27942,7 +27948,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -28078,7 +28084,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -28094,7 +28100,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -32629,7 +32635,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1621</v>
       </c>
     </row>
@@ -32645,7 +32651,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -32902,7 +32908,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -32918,7 +32924,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33207,7 +33213,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33223,7 +33229,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33359,7 +33365,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33375,7 +33381,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33511,7 +33517,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33527,7 +33533,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33663,7 +33669,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33679,7 +33685,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33824,7 +33830,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -33840,7 +33846,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -34053,7 +34059,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -34069,7 +34075,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -34205,7 +34211,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -34221,7 +34227,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -34632,7 +34638,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -34648,7 +34654,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -37985,7 +37991,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38001,7 +38007,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38336,7 +38342,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38352,7 +38358,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38531,7 +38537,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38547,7 +38553,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38683,7 +38689,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38699,7 +38705,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38874,7 +38880,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -38890,7 +38896,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -39026,7 +39032,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1676</v>
       </c>
     </row>
@@ -39042,7 +39048,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>1678</v>
       </c>
     </row>
@@ -39378,7 +39384,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -39394,7 +39400,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -39569,7 +39575,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -39585,7 +39591,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -39721,7 +39727,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1690</v>
       </c>
     </row>
@@ -39737,7 +39743,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40066,7 +40072,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40082,7 +40088,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40218,7 +40224,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40234,7 +40240,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40370,7 +40376,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40386,7 +40392,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40631,7 +40637,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40647,7 +40653,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40783,7 +40789,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40799,7 +40805,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40935,7 +40941,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -40951,7 +40957,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -41087,7 +41093,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -41103,7 +41109,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -41239,7 +41245,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1710</v>
       </c>
     </row>
@@ -41255,7 +41261,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -41620,7 +41626,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -41636,7 +41642,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -42298,7 +42304,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1726</v>
       </c>
     </row>
@@ -42314,7 +42320,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -42604,7 +42610,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -42620,7 +42626,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -42756,7 +42762,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -42772,7 +42778,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43073,7 +43079,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43089,7 +43095,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43348,7 +43354,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43364,7 +43370,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43711,7 +43717,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43727,7 +43733,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43863,7 +43869,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -43879,7 +43885,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44015,7 +44021,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44031,7 +44037,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44167,7 +44173,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44183,7 +44189,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44319,7 +44325,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44335,7 +44341,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44689,7 +44695,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44705,7 +44711,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -44830,7 +44836,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1765</v>
       </c>
     </row>
@@ -44846,7 +44852,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -45249,7 +45255,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1779</v>
       </c>
     </row>
@@ -45265,7 +45271,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -45990,7 +45996,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46006,7 +46012,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46131,7 +46137,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46147,7 +46153,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46639,7 +46645,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46655,7 +46661,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46780,7 +46786,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46796,7 +46802,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46921,7 +46927,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -46937,7 +46943,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47431,7 +47437,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47447,7 +47453,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47572,7 +47578,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47588,7 +47594,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47713,7 +47719,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47729,7 +47735,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47865,7 +47871,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -47881,7 +47887,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>1804</v>
       </c>
     </row>
@@ -48017,7 +48023,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48033,7 +48039,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48169,7 +48175,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48185,7 +48191,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48321,7 +48327,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48337,7 +48343,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48462,7 +48468,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1513</v>
       </c>
     </row>
@@ -48478,7 +48484,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48865,7 +48871,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -48881,7 +48887,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49017,7 +49023,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49033,7 +49039,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49169,7 +49175,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1812</v>
       </c>
     </row>
@@ -49185,7 +49191,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49348,7 +49354,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49364,7 +49370,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49489,7 +49495,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1822</v>
       </c>
     </row>
@@ -49505,7 +49511,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49641,7 +49647,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49657,7 +49663,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49793,7 +49799,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49809,7 +49815,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -49945,7 +49951,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>1829</v>
       </c>
     </row>
@@ -49961,7 +49967,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -50145,7 +50151,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -50161,7 +50167,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -50414,7 +50420,7 @@
       <c r="A5" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>700</v>
       </c>
     </row>
@@ -50430,7 +50436,7 @@
       <c r="A7" s="5" t="s">
         <v>1479</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>700</v>
       </c>
     </row>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13080,7 +13080,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-02-12T20:36:41.868894+00:00</t>
+    <t>2026-03-15T17:06:47.925690+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13080,7 +13080,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-15T17:06:47.925690+00:00</t>
+    <t>2026-03-15T17:10:50.795633+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>

--- a/.repo_info/solve-it-latest.xlsx
+++ b/.repo_info/solve-it-latest.xlsx
@@ -13080,7 +13080,7 @@
     <t>Workbook generated</t>
   </si>
   <si>
-    <t>2026-03-15T17:10:50.795633+00:00</t>
+    <t>2026-03-15T17:12:50.264148+00:00</t>
   </si>
   <si>
     <t>Number of objectives</t>
